--- a/docs/d/229/inyear.xlsx
+++ b/docs/d/229/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$160</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 67 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 66 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA159"/>
+  <dimension ref="A1:AA160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1461,8 +1461,8 @@
       <c r="P8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="9" t="n">
-        <v>1</v>
+      <c r="Q8" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R8" s="9" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2264,8 +2264,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>7</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6135,8 +6135,8 @@
       <c r="V56" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W56" s="9" t="n">
-        <v>3</v>
+      <c r="W56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>7</v>
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="P103" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X128" s="9" t="n">
         <v>3</v>
@@ -13244,15 +13244,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>7423799</v>
+        <v>28680951</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Hexaware Chennai Toastmasters</t>
+          <t>Fuso Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13266,10 +13266,10 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0</v>
@@ -13293,16 +13293,16 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q130" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S130" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T130" s="9" t="n">
         <v>0</v>
@@ -13316,14 +13316,14 @@
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X130" s="10" t="n">
-        <v>7</v>
+      <c r="X130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -13341,15 +13341,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>7218703</v>
+        <v>7423799</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Hillview Toastmasters Club</t>
+          <t>Hexaware Chennai Toastmasters</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13363,17 +13363,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L131" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M131" s="7" t="n">
@@ -13390,7 +13390,7 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q131" s="9" t="n">
         <v>1</v>
@@ -13399,7 +13399,7 @@
         <v>0</v>
       </c>
       <c r="S131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131" s="9" t="n">
         <v>0</v>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -13419,8 +13419,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="10" t="n">
-        <v>1</v>
+      <c r="Z131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -13438,39 +13438,39 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>7906864</v>
+        <v>7218703</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Puducherry Toastmasters Club</t>
+          <t>Hillview Toastmasters Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J132" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K132" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F132" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G132" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I132" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J132" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L132" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M132" s="7" t="n">
@@ -13496,16 +13496,16 @@
         <v>0</v>
       </c>
       <c r="S132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T132" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T132" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -13535,15 +13535,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28679657</v>
+        <v>7906864</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>SMVEC Toastmasters Club</t>
+          <t>Puducherry Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,10 +13557,10 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K133" s="4" t="n">
         <v>0</v>
@@ -13584,19 +13584,19 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q133" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R133" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="Q133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S133" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
@@ -13628,19 +13628,19 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>28677226</v>
+        <v>28679657</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Acxhange Articulation Club</t>
+          <t>SMVEC Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,10 +13654,10 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K134" s="4" t="n">
         <v>0</v>
@@ -13681,16 +13681,16 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q134" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T134" s="9" t="n">
         <v>0</v>
@@ -13704,14 +13704,14 @@
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X134" s="9" t="n">
-        <v>0</v>
+      <c r="X134" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -13729,11 +13729,11 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>28678561</v>
+        <v>28677226</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>CIT Toastmasters Club</t>
+          <t>Acxhange Articulation Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
@@ -13751,25 +13751,25 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="K135" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L135" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O135" s="8" t="inlineStr">
@@ -13810,8 +13810,8 @@
       <c r="Z135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA135" s="9" t="n">
-        <v>0</v>
+      <c r="AA135" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -13826,11 +13826,11 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>6728365</v>
+        <v>28678561</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Downtown Speakers Forum</t>
+          <t>CIT Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L136" s="8" t="inlineStr">
         <is>
@@ -13862,11 +13862,11 @@
         </is>
       </c>
       <c r="M136" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O136" s="8" t="inlineStr">
@@ -13893,13 +13893,13 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X136" s="10" t="n">
-        <v>7</v>
+      <c r="X136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
@@ -13907,8 +13907,8 @@
       <c r="Z136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA136" s="10" t="n">
-        <v>1</v>
+      <c r="AA136" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -13923,15 +13923,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>28677562</v>
+        <v>6728365</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>East Tambaram Speakers Forum</t>
+          <t>Downtown Speakers Forum</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,17 +13945,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="7" t="n">
@@ -13972,10 +13972,10 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q137" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R137" s="9" t="n">
         <v>0</v>
@@ -13989,11 +13989,11 @@
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="10" t="n">
-        <v>4</v>
+      <c r="V137" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>7</v>
@@ -14001,8 +14001,8 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="10" t="n">
-        <v>1</v>
+      <c r="Z137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14020,15 +14020,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>28679619</v>
+        <v>28677562</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Ramco Toastmasters Club</t>
+          <t>East Tambaram Speakers Forum</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14069,10 +14069,10 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
@@ -14086,20 +14086,20 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>0</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X138" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="X138" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14117,15 +14117,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>28678560</v>
+        <v>28679619</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>RNAIPL Toastmasters Club</t>
+          <t>Ramco Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
@@ -14189,14 +14189,14 @@
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X139" s="10" t="n">
-        <v>6</v>
+      <c r="X139" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="10" t="n">
-        <v>1</v>
+      <c r="Z139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14205,20 +14205,20 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>28678104</v>
+        <v>28678560</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Caterpillar BCP Orators Toastmasters Club</t>
+          <t>RNAIPL Toastmasters Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
@@ -14236,17 +14236,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M140" s="7" t="n">
@@ -14265,8 +14265,8 @@
       <c r="P140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" s="10" t="n">
-        <v>2</v>
+      <c r="Q140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R140" s="9" t="n">
         <v>0</v>
@@ -14287,13 +14287,13 @@
         <v>0</v>
       </c>
       <c r="X140" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -14311,15 +14311,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>6545042</v>
+        <v>28678104</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Chennai Champions Toastmasters</t>
+          <t>Caterpillar BCP Orators Toastmasters Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14333,17 +14333,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L141" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M141" s="7" t="n">
@@ -14359,17 +14359,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P141" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q141" s="9" t="n">
-        <v>0</v>
+      <c r="P141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S141" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T141" s="9" t="n">
         <v>0</v>
@@ -14377,20 +14377,20 @@
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W141" s="10" t="n">
+      <c r="V141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="X141" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="10" t="n">
-        <v>1</v>
+      <c r="Z141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -14408,15 +14408,15 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>7786564</v>
+        <v>6545042</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Leaders Forum Toastmasters Club</t>
+          <t>Chennai Champions Toastmasters</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -14456,8 +14456,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P142" s="9" t="n">
-        <v>1</v>
+      <c r="P142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -14466,22 +14466,22 @@
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T142" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W142" s="9" t="n">
-        <v>0</v>
+      <c r="V142" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W142" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X142" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
@@ -14505,15 +14505,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>8001232</v>
+        <v>7786564</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>REC Toastmasters Club</t>
+          <t>Dynamic Leaders Forum Toastmasters Club</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14565,14 +14565,14 @@
       <c r="S143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T143" s="9" t="n">
-        <v>0</v>
+      <c r="T143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -14602,15 +14602,15 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>6633002</v>
+        <v>8001232</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>RNTBCI Toastmasters Club</t>
+          <t>REC Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,25 +14624,25 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K144" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L144" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M144" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N144" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O144" s="8" t="inlineStr">
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -14674,17 +14674,17 @@
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X144" s="9" t="n">
-        <v>0</v>
+      <c r="X144" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA144" s="9" t="n">
-        <v>0</v>
+      <c r="Z144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA144" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -14699,15 +14699,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>6879130</v>
+        <v>6633002</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Vellore Toastmasters Club</t>
+          <t>RNTBCI Toastmasters Club</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,25 +14721,25 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K145" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L145" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M145" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O145" s="8" t="inlineStr">
@@ -14748,19 +14748,19 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q145" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q145" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S145" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T145" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T145" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U145" s="9" t="n">
         <v>0</v>
@@ -14771,17 +14771,17 @@
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X145" s="10" t="n">
-        <v>7</v>
+      <c r="X145" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA145" s="10" t="n">
-        <v>1</v>
+      <c r="Z145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -14792,15 +14792,15 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>3295314</v>
+        <v>6879130</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Agua VIT</t>
+          <t>Vellore Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -14818,17 +14818,17 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K146" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L146" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M146" s="7" t="n">
@@ -14847,8 +14847,8 @@
       <c r="P146" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q146" s="9" t="n">
-        <v>0</v>
+      <c r="Q146" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
@@ -14859,8 +14859,8 @@
       <c r="T146" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U146" s="10" t="n">
-        <v>1</v>
+      <c r="U146" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="X146" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
@@ -14893,15 +14893,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>2677403</v>
+        <v>3295314</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Clima VIT</t>
+          <t>Agua VIT</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,17 +14915,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K147" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M147" s="7" t="n">
@@ -14942,7 +14942,7 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q147" s="9" t="n">
         <v>0</v>
@@ -14950,14 +14950,14 @@
       <c r="R147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S147" s="10" t="n">
-        <v>2</v>
+      <c r="S147" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="T147" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U147" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V147" s="9" t="n">
         <v>0</v>
@@ -14990,11 +14990,11 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>3295556</v>
+        <v>2677403</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Fogo VIT</t>
+          <t>Clima VIT</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
@@ -15012,10 +15012,10 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K148" s="4" t="n">
         <v>0</v>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q148" s="9" t="n">
         <v>0</v>
@@ -15048,13 +15048,13 @@
         <v>0</v>
       </c>
       <c r="S148" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T148" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U148" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V148" s="9" t="n">
         <v>0</v>
@@ -15063,7 +15063,7 @@
         <v>0</v>
       </c>
       <c r="X148" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
@@ -15087,15 +15087,15 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>4198323</v>
+        <v>3295556</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Nuvens VIT</t>
+          <t>Fogo VIT</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15109,17 +15109,17 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K149" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L149" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M149" s="7" t="n">
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>0</v>
@@ -15145,13 +15145,13 @@
         <v>0</v>
       </c>
       <c r="S149" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T149" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U149" s="9" t="n">
-        <v>0</v>
+      <c r="U149" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="V149" s="9" t="n">
         <v>0</v>
@@ -15184,15 +15184,15 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>4198235</v>
+        <v>4198323</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Phoenix VIT</t>
+          <t>Nuvens VIT</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K150" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M150" s="7" t="n">
@@ -15241,11 +15241,11 @@
       <c r="R150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" s="9" t="n">
-        <v>0</v>
+      <c r="S150" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U150" s="9" t="n">
         <v>0</v>
@@ -15277,19 +15277,19 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>2677376</v>
+        <v>4198235</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Brisa VIT</t>
+          <t>Phoenix VIT</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15303,17 +15303,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K151" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L151" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -15339,10 +15339,10 @@
         <v>0</v>
       </c>
       <c r="S151" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T151" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U151" s="9" t="n">
         <v>0</v>
@@ -15378,11 +15378,11 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>5073498</v>
+        <v>2677376</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Ora VIT Toastmasters</t>
+          <t>Brisa VIT</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -15400,17 +15400,17 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K152" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L152" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M152" s="7" t="n">
@@ -15427,7 +15427,7 @@
         </is>
       </c>
       <c r="P152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q152" s="9" t="n">
         <v>0</v>
@@ -15436,7 +15436,7 @@
         <v>0</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152" s="9" t="n">
         <v>0</v>
@@ -15451,7 +15451,7 @@
         <v>0</v>
       </c>
       <c r="X152" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
@@ -15475,15 +15475,15 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>5125333</v>
+        <v>5073498</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Sol VIT</t>
+          <t>Ora VIT Toastmasters</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15497,17 +15497,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L153" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M153" s="7" t="n">
@@ -15524,31 +15524,31 @@
         </is>
       </c>
       <c r="P153" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q153" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S153" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U153" s="10" t="n">
-        <v>2</v>
+      <c r="S153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X153" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
@@ -15572,15 +15572,15 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>1600941</v>
+        <v>5125333</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Terra VIT</t>
+          <t>Sol VIT</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15594,17 +15594,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L154" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="7" t="n">
@@ -15621,37 +15621,37 @@
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U154" s="9" t="n">
-        <v>0</v>
+      <c r="S154" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U154" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X154" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -15669,15 +15669,15 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>6882850</v>
+        <v>1600941</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>TRUENO VIT</t>
+          <t>Terra VIT</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -15691,10 +15691,10 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K155" s="4" t="n">
         <v>0</v>
@@ -15718,19 +15718,19 @@
         </is>
       </c>
       <c r="P155" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q155" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R155" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T155" s="10" t="n">
-        <v>1</v>
+      <c r="T155" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U155" s="9" t="n">
         <v>0</v>
@@ -15742,13 +15742,13 @@
         <v>0</v>
       </c>
       <c r="X155" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="10" t="n">
-        <v>1</v>
+      <c r="Z155" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -15762,15 +15762,15 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>28676603</v>
+        <v>6882850</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Avadi Impeccable Speakers Toastmasters Club</t>
+          <t>TRUENO VIT</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
@@ -15814,14 +15814,14 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P156" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q156" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R156" s="9" t="n">
-        <v>0</v>
+      <c r="P156" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q156" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R156" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S156" s="9" t="n">
         <v>0</v>
@@ -15832,8 +15832,8 @@
       <c r="U156" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V156" s="10" t="n">
-        <v>4</v>
+      <c r="V156" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -15863,15 +15863,15 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>2072381</v>
+        <v>28676603</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>CatMiner Toastmasters Club</t>
+          <t>Avadi Impeccable Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -15911,17 +15911,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P157" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q157" s="10" t="n">
-        <v>2</v>
+      <c r="P157" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q157" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S157" s="10" t="n">
-        <v>2</v>
+      <c r="S157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T157" s="10" t="n">
         <v>1</v>
@@ -15933,7 +15933,7 @@
         <v>4</v>
       </c>
       <c r="W157" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X157" s="10" t="n">
         <v>7</v>
@@ -15960,15 +15960,15 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>4935335</v>
+        <v>2072381</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>DICV Toastmasters</t>
+          <t>CatMiner Toastmasters Club</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -15982,17 +15982,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M158" s="7" t="n">
@@ -16009,37 +16009,37 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q158" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q158" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V158" s="9" t="n">
-        <v>0</v>
+      <c r="S158" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V158" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W158" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X158" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA158" s="10" t="n">
         <v>1</v>
@@ -16057,11 +16057,11 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>6899839</v>
+        <v>4935335</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Panimalar Toastmasters Club</t>
+          <t>DICV Toastmasters</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L159" s="8" t="inlineStr">
         <is>
@@ -16124,26 +16124,123 @@
         <v>0</v>
       </c>
       <c r="V159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="n">
+        <v>6899839</v>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>Panimalar Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G160" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J160" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K160" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W159" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X159" s="10" t="n">
+      <c r="L160" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M160" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O160" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Y159" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA159" s="10" t="n">
+      <c r="Y160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA160" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA159"/>
+  <autoFilter ref="A1:AA160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16263,7 +16360,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16329,7 +16426,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -16593,7 +16690,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -17151,25 +17248,25 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>4</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>4</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -17253,7 +17350,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -17286,13 +17383,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>

--- a/docs/d/229/inyear.xlsx
+++ b/docs/d/229/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/229/inyear.xlsx
+++ b/docs/d/229/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 66 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 61 clubs short</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
         <v>2</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="9" t="n">
         <v>1</v>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="P11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="9" t="n">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="9" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2440,8 +2440,8 @@
       <c r="S18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T18" s="9" t="n">
-        <v>0</v>
+      <c r="T18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3216,8 +3216,8 @@
       <c r="S26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T26" s="9" t="n">
-        <v>0</v>
+      <c r="T26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U26" s="9" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3331,8 +3331,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6114,11 +6114,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P56" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="9" t="n">
-        <v>1</v>
+      <c r="P56" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q56" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6517,8 +6517,8 @@
       <c r="T60" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U60" s="9" t="n">
-        <v>0</v>
+      <c r="U60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V60" s="10" t="n">
         <v>4</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8084,8 +8084,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8666,8 +8666,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9122,16 +9122,16 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" s="9" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9430,11 +9430,11 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>1</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>4</v>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10300,8 +10300,8 @@
       <c r="T99" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U99" s="9" t="n">
-        <v>0</v>
+      <c r="U99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V99" s="9" t="n">
         <v>0</v>
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="P103" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -10683,7 +10683,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T103" s="10" t="n">
         <v>1</v>
@@ -11700,7 +11700,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11743,8 +11743,8 @@
       <c r="P114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" s="9" t="n">
-        <v>1</v>
+      <c r="Q114" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>0</v>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13401,8 +13401,8 @@
       <c r="S131" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T131" s="9" t="n">
-        <v>0</v>
+      <c r="T131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U131" s="9" t="n">
         <v>0</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14389,8 +14389,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -14942,7 +14942,7 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q147" s="9" t="n">
         <v>0</v>
@@ -15054,7 +15054,7 @@
         <v>1</v>
       </c>
       <c r="U148" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V148" s="9" t="n">
         <v>0</v>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>0</v>
@@ -15145,13 +15145,13 @@
         <v>0</v>
       </c>
       <c r="S149" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T149" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U149" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V149" s="9" t="n">
         <v>0</v>
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15344,8 +15344,8 @@
       <c r="T151" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U151" s="9" t="n">
-        <v>0</v>
+      <c r="U151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V151" s="9" t="n">
         <v>0</v>
@@ -15677,7 +15677,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -15747,8 +15747,8 @@
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -15824,13 +15824,13 @@
         <v>2</v>
       </c>
       <c r="S156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T156" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U156" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V156" s="9" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16203,10 +16203,10 @@
         </is>
       </c>
       <c r="P160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
@@ -16214,8 +16214,8 @@
       <c r="S160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T160" s="9" t="n">
-        <v>0</v>
+      <c r="T160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U160" s="9" t="n">
         <v>0</v>
@@ -16426,7 +16426,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -16492,7 +16492,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16690,13 +16690,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -16723,13 +16723,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -16822,7 +16822,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16888,7 +16888,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16921,7 +16921,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16987,7 +16987,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17119,7 +17119,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17251,7 +17251,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -17317,7 +17317,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -17350,7 +17350,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -17383,7 +17383,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -17416,7 +17416,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>

--- a/docs/d/229/inyear.xlsx
+++ b/docs/d/229/inyear.xlsx
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 43 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,20 +850,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -871,7 +871,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -947,20 +947,20 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8" t="inlineStr">
+        <v>-11</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M3" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -968,7 +968,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1044,20 +1044,20 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1141,20 +1141,20 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1162,7 +1162,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1251,7 +1251,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1259,7 +1259,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1335,20 +1335,20 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1356,7 +1356,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1383,7 +1383,7 @@
         <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" s="10" t="n">
         <v>7</v>
@@ -1432,34 +1432,34 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K8" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="Q8" s="10" t="n">
         <v>2</v>
@@ -1477,7 +1477,7 @@
         <v>2</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1529,20 +1529,20 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1550,7 +1550,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1573,11 +1573,11 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>0</v>
+      <c r="V9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>7</v>
@@ -1626,20 +1626,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1723,20 +1723,20 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1744,7 +1744,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1820,34 +1820,34 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K12" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P12" s="10" t="n">
-        <v>4</v>
       </c>
       <c r="Q12" s="10" t="n">
         <v>2</v>
@@ -1917,20 +1917,20 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1938,7 +1938,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1947,7 +1947,7 @@
         <v>3</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2014,20 +2014,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2035,7 +2035,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2058,11 +2058,11 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>0</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>5</v>
@@ -2111,20 +2111,20 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2208,20 +2208,20 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2229,7 +2229,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>0</v>
@@ -2252,11 +2252,11 @@
       <c r="U16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="9" t="n">
-        <v>0</v>
+      <c r="V16" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>7</v>
@@ -2305,20 +2305,20 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2326,7 +2326,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2353,7 +2353,7 @@
         <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>7</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2402,20 +2402,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2423,7 +2423,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2449,8 +2449,8 @@
       <c r="V18" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W18" s="9" t="n">
-        <v>1</v>
+      <c r="W18" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X18" s="10" t="n">
         <v>7</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2512,7 +2512,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2520,13 +2520,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P19" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="10" t="n">
         <v>2</v>
@@ -2534,8 +2534,8 @@
       <c r="R19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="9" t="n">
-        <v>1</v>
+      <c r="S19" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T19" s="10" t="n">
         <v>1</v>
@@ -2546,8 +2546,8 @@
       <c r="V19" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W19" s="9" t="n">
-        <v>2</v>
+      <c r="W19" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>6</v>
@@ -2596,20 +2596,20 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2617,7 +2617,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2693,20 +2693,20 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2714,7 +2714,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2790,20 +2790,20 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2811,7 +2811,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2887,20 +2887,20 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2908,7 +2908,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2984,20 +2984,20 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -3005,7 +3005,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3081,20 +3081,20 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -3102,7 +3102,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3125,11 +3125,11 @@
       <c r="U25" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>1</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X25" s="9" t="n">
         <v>2</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3178,20 +3178,20 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3199,7 +3199,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3222,8 +3222,8 @@
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="9" t="n">
-        <v>3</v>
+      <c r="V26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3275,20 +3275,20 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3296,7 +3296,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3372,20 +3372,20 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3414,7 +3414,7 @@
         <v>1</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V28" s="9" t="n">
         <v>2</v>
@@ -3469,20 +3469,20 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3490,7 +3490,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3566,20 +3566,20 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3587,7 +3587,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3601,8 +3601,8 @@
       <c r="R30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S30" s="9" t="n">
-        <v>1</v>
+      <c r="S30" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T30" s="10" t="n">
         <v>1</v>
@@ -3663,20 +3663,20 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="8" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3684,7 +3684,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3773,7 +3773,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3781,7 +3781,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3857,20 +3857,20 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M33" s="7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3878,7 +3878,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3954,20 +3954,20 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M34" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3975,7 +3975,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4051,20 +4051,20 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4</v>
+        <v>-17</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4072,13 +4072,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q35" s="10" t="n">
         <v>2</v>
@@ -4148,20 +4148,20 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4169,7 +4169,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4245,20 +4245,20 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4266,7 +4266,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4289,11 +4289,11 @@
       <c r="U37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="9" t="n">
-        <v>0</v>
+      <c r="V37" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W37" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>6</v>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4342,20 +4342,20 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4363,7 +4363,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4383,8 +4383,8 @@
       <c r="T38" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U38" s="9" t="n">
-        <v>0</v>
+      <c r="U38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V38" s="10" t="n">
         <v>4</v>
@@ -4439,20 +4439,20 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4460,7 +4460,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4549,7 +4549,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4557,7 +4557,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4633,20 +4633,20 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4654,7 +4654,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4730,20 +4730,20 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M42" s="7" t="n">
+      <c r="M42" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4751,7 +4751,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4778,7 +4778,7 @@
         <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>7</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -4840,7 +4840,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="M43" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4848,7 +4848,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4871,11 +4871,11 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="9" t="n">
-        <v>0</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W43" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>5</v>
@@ -4924,20 +4924,20 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
+        <v>-11</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4945,7 +4945,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5021,20 +5021,20 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5042,7 +5042,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5126,12 +5126,12 @@
       <c r="K46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L46" s="8" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="M46" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5139,7 +5139,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5215,20 +5215,20 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="M47" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5236,7 +5236,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5312,20 +5312,20 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>5</v>
+        <v>-12</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5333,7 +5333,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="10" t="n">
         <v>1</v>
@@ -5409,20 +5409,20 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5430,7 +5430,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5506,20 +5506,20 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5527,7 +5527,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5553,8 +5553,8 @@
       <c r="V50" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W50" s="9" t="n">
-        <v>3</v>
+      <c r="W50" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>7</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5603,20 +5603,20 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="M51" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5624,7 +5624,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5647,11 +5647,11 @@
       <c r="U51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="9" t="n">
-        <v>0</v>
+      <c r="V51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>5</v>
@@ -5659,8 +5659,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5700,20 +5700,20 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M52" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M52" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5721,7 +5721,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5744,11 +5744,11 @@
       <c r="U52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="9" t="n">
-        <v>0</v>
+      <c r="V52" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X52" s="9" t="n">
         <v>2</v>
@@ -5805,12 +5805,12 @@
       <c r="K53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L53" s="8" t="inlineStr">
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M53" s="7" t="n">
+      <c r="M53" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5818,7 +5818,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5894,20 +5894,20 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M54" s="7" t="n">
+        <v>-38</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M54" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5915,7 +5915,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5991,20 +5991,20 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M55" s="7" t="n">
+      <c r="M55" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6012,7 +6012,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6036,7 +6036,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6101,7 +6101,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M56" s="7" t="n">
+      <c r="M56" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6109,7 +6109,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6185,20 +6185,20 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>8</v>
+        <v>-7</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M57" s="7" t="n">
+      <c r="M57" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6206,7 +6206,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6218,7 +6218,7 @@
         <v>2</v>
       </c>
       <c r="R57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" s="9" t="n">
         <v>0</v>
@@ -6233,7 +6233,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>7</v>
@@ -6290,12 +6290,12 @@
       <c r="K58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L58" s="8" t="inlineStr">
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="M58" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -6303,7 +6303,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6379,20 +6379,20 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M59" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M59" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6400,7 +6400,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6476,20 +6476,20 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L60" s="8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M60" s="7" t="n">
+      <c r="M60" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6497,13 +6497,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -6520,11 +6520,11 @@
       <c r="U60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="9" t="n">
-        <v>3</v>
+      <c r="V60" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>7</v>
@@ -6573,20 +6573,20 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="M61" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6594,7 +6594,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6683,7 +6683,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M62" s="7" t="n">
+      <c r="M62" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -6691,7 +6691,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6767,20 +6767,20 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6788,16 +6788,16 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
@@ -6811,11 +6811,11 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>0</v>
+      <c r="V63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>7</v>
@@ -6864,20 +6864,20 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>9</v>
+        <v>-4</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M64" s="7" t="n">
+      <c r="M64" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -6885,7 +6885,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6961,20 +6961,20 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M65" s="7" t="n">
+      <c r="M65" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6982,7 +6982,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7058,20 +7058,20 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7079,7 +7079,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7155,20 +7155,20 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M67" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M67" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -7176,7 +7176,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O67" s="8" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7252,20 +7252,20 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7273,7 +7273,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7349,20 +7349,20 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="M69" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7370,7 +7370,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7393,8 +7393,8 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>0</v>
+      <c r="V69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7446,20 +7446,20 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M70" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7467,7 +7467,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7543,20 +7543,20 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -7564,7 +7564,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -7640,20 +7640,20 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
+        <v>-18</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M72" s="7" t="n">
+      <c r="M72" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -7661,7 +7661,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7737,20 +7737,20 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M73" s="7" t="n">
+      <c r="M73" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7758,7 +7758,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7834,20 +7834,20 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M74" s="7" t="n">
+      <c r="M74" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -7855,7 +7855,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7931,20 +7931,20 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M75" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M75" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -7952,7 +7952,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8028,20 +8028,20 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M76" s="7" t="n">
+      <c r="M76" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8049,7 +8049,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8125,20 +8125,20 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M77" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M77" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8146,7 +8146,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8222,20 +8222,20 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M78" s="7" t="n">
+      <c r="M78" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8243,7 +8243,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8319,20 +8319,20 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M79" s="7" t="n">
+      <c r="M79" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8340,7 +8340,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8364,7 +8364,7 @@
         <v>1</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8416,20 +8416,20 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="8" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M80" s="7" t="n">
+      <c r="M80" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8437,7 +8437,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8513,20 +8513,20 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M81" s="7" t="n">
+      <c r="M81" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -8534,7 +8534,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O81" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8610,20 +8610,20 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L82" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M82" s="7" t="n">
+      <c r="M82" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -8631,7 +8631,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8707,20 +8707,20 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M83" s="7" t="n">
+      <c r="M83" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -8728,7 +8728,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8755,7 +8755,7 @@
         <v>4</v>
       </c>
       <c r="W83" s="10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>5</v>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8804,38 +8804,38 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K84" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O84" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M84" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N84" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O84" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
       </c>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8901,20 +8901,20 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M85" s="7" t="n">
+      <c r="M85" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -8922,7 +8922,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O85" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8945,8 +8945,8 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>0</v>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -8998,20 +8998,20 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M86" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M86" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9019,7 +9019,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="O86" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9043,7 +9043,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9095,20 +9095,20 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M87" s="7" t="n">
+      <c r="M87" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9116,13 +9116,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>0</v>
@@ -9139,11 +9139,11 @@
       <c r="U87" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>1</v>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>5</v>
@@ -9192,20 +9192,20 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M88" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M88" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -9213,7 +9213,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9297,12 +9297,12 @@
       <c r="K89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L89" s="8" t="inlineStr">
+      <c r="L89" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M89" s="7" t="n">
+      <c r="M89" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9310,7 +9310,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9386,20 +9386,20 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="8" t="inlineStr">
+        <v>-13</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="M90" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9407,7 +9407,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9483,20 +9483,20 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="M91" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -9504,7 +9504,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9580,20 +9580,20 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M92" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M92" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -9601,7 +9601,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="O92" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9610,7 +9610,7 @@
         <v>2</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9677,20 +9677,20 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M93" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M93" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -9698,7 +9698,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9721,11 +9721,11 @@
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" s="9" t="n">
-        <v>0</v>
+      <c r="V93" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W93" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>6</v>
@@ -9774,20 +9774,20 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M94" s="7" t="n">
+      <c r="M94" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -9795,7 +9795,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="O94" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9871,20 +9871,20 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M95" s="7" t="n">
+        <v>-33</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M95" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -9892,7 +9892,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9976,12 +9976,12 @@
       <c r="K96" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L96" s="8" t="inlineStr">
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M96" s="7" t="n">
+      <c r="M96" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -9989,7 +9989,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10013,7 +10013,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,20 +10065,20 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M97" s="7" t="n">
+      <c r="M97" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10086,16 +10086,16 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="O97" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10109,11 +10109,11 @@
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" s="9" t="n">
-        <v>0</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W97" s="10" t="n">
+        <v>17</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>7</v>
@@ -10162,20 +10162,20 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M98" s="7" t="n">
+      <c r="M98" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10183,7 +10183,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10207,7 +10207,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10259,20 +10259,20 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M99" s="7" t="n">
+      <c r="M99" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10280,7 +10280,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10356,20 +10356,20 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M100" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M100" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -10377,7 +10377,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="O100" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10389,7 +10389,7 @@
         <v>2</v>
       </c>
       <c r="R100" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S100" s="9" t="n">
         <v>1</v>
@@ -10453,20 +10453,20 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M101" s="7" t="n">
+      <c r="M101" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -10474,7 +10474,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O101" s="8" t="inlineStr">
+      <c r="O101" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10550,20 +10550,20 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M102" s="7" t="n">
+      <c r="M102" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -10571,7 +10571,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O102" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10660,7 +10660,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M103" s="7" t="n">
+      <c r="M103" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -10668,7 +10668,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="O103" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,20 +10744,20 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M104" s="7" t="n">
+      <c r="M104" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -10765,7 +10765,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O104" s="8" t="inlineStr">
+      <c r="O104" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10780,16 +10780,16 @@
         <v>0</v>
       </c>
       <c r="S104" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="T104" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,20 +10841,20 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M105" s="7" t="n">
+      <c r="M105" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -10862,13 +10862,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O105" s="8" t="inlineStr">
+      <c r="O105" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -10877,19 +10877,19 @@
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U105" s="9" t="n">
-        <v>0</v>
+      <c r="U105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V105" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W105" s="9" t="n">
-        <v>0</v>
+      <c r="W105" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -10938,20 +10938,20 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M106" s="7" t="n">
+      <c r="M106" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -10959,13 +10959,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O106" s="8" t="inlineStr">
+      <c r="O106" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>1</v>
@@ -11048,7 +11048,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M107" s="7" t="n">
+      <c r="M107" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -11056,7 +11056,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O107" s="8" t="inlineStr">
+      <c r="O107" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,43 +11132,43 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K108" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M108" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O108" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P108" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M108" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N108" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O108" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P108" s="9" t="n">
+      <c r="Q108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="Q108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" s="10" t="n">
-        <v>2</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,55 +11229,55 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K109" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M109" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O109" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W109" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M109" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N109" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O109" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T109" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V109" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W109" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -11326,20 +11326,20 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M110" s="7" t="n">
+      <c r="M110" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
@@ -11347,7 +11347,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O110" s="8" t="inlineStr">
+      <c r="O110" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11423,20 +11423,20 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M111" s="7" t="n">
+      <c r="M111" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -11444,7 +11444,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O111" s="8" t="inlineStr">
+      <c r="O111" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11468,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -11520,20 +11520,20 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M112" s="7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M112" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
@@ -11541,7 +11541,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O112" s="8" t="inlineStr">
+      <c r="O112" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11617,20 +11617,20 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M113" s="7" t="n">
+      <c r="M113" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -11638,7 +11638,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O113" s="8" t="inlineStr">
+      <c r="O113" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11665,7 +11665,7 @@
         <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X113" s="10" t="n">
         <v>7</v>
@@ -11727,7 +11727,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M114" s="7" t="n">
+      <c r="M114" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -11735,7 +11735,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O114" s="8" t="inlineStr">
+      <c r="O114" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11811,20 +11811,20 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M115" s="7" t="n">
+      <c r="M115" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -11832,7 +11832,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O115" s="8" t="inlineStr">
+      <c r="O115" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11908,20 +11908,20 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M116" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M116" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -11929,7 +11929,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O116" s="8" t="inlineStr">
+      <c r="O116" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11953,7 +11953,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       <c r="K117" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L117" s="8" t="inlineStr">
+      <c r="L117" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M117" s="7" t="n">
+      <c r="M117" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -12026,7 +12026,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O117" s="8" t="inlineStr">
+      <c r="O117" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12115,7 +12115,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M118" s="7" t="n">
+      <c r="M118" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
@@ -12123,7 +12123,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O118" s="8" t="inlineStr">
+      <c r="O118" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12146,11 +12146,11 @@
       <c r="U118" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" s="9" t="n">
-        <v>0</v>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>7</v>
@@ -12158,8 +12158,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12199,20 +12199,20 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M119" s="7" t="n">
+      <c r="M119" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -12220,7 +12220,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O119" s="8" t="inlineStr">
+      <c r="O119" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12235,7 +12235,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119" s="10" t="n">
         <v>1</v>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12309,7 +12309,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M120" s="7" t="n">
+      <c r="M120" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
@@ -12317,7 +12317,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O120" s="8" t="inlineStr">
+      <c r="O120" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12343,8 +12343,8 @@
       <c r="V120" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W120" s="9" t="n">
-        <v>3</v>
+      <c r="W120" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>7</v>
@@ -12406,7 +12406,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M121" s="7" t="n">
+      <c r="M121" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -12414,7 +12414,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O121" s="8" t="inlineStr">
+      <c r="O121" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12490,20 +12490,20 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M122" s="7" t="n">
+      <c r="M122" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -12511,13 +12511,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O122" s="8" t="inlineStr">
+      <c r="O122" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -12587,20 +12587,20 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M123" s="7" t="n">
+      <c r="M123" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -12608,7 +12608,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O123" s="8" t="inlineStr">
+      <c r="O123" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,20 +12684,20 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M124" s="7" t="n">
+      <c r="M124" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -12705,7 +12705,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O124" s="8" t="inlineStr">
+      <c r="O124" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12731,8 +12731,8 @@
       <c r="V124" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W124" s="9" t="n">
-        <v>1</v>
+      <c r="W124" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>7</v>
@@ -12781,20 +12781,20 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L125" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M125" s="7" t="n">
+      <c r="M125" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -12802,7 +12802,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O125" s="8" t="inlineStr">
+      <c r="O125" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12878,20 +12878,20 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L126" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M126" s="7" t="n">
+      <c r="M126" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
@@ -12899,7 +12899,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O126" s="8" t="inlineStr">
+      <c r="O126" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12926,7 +12926,7 @@
         <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>5</v>
@@ -12975,20 +12975,20 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M127" s="7" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M127" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
@@ -12996,7 +12996,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O127" s="8" t="inlineStr">
+      <c r="O127" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13080,12 +13080,12 @@
       <c r="K128" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L128" s="8" t="inlineStr">
+      <c r="L128" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M128" s="7" t="n">
+      <c r="M128" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N128" s="4" t="inlineStr">
@@ -13093,7 +13093,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O128" s="8" t="inlineStr">
+      <c r="O128" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13117,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13169,20 +13169,20 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M129" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M129" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
@@ -13190,7 +13190,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O129" s="8" t="inlineStr">
+      <c r="O129" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13266,20 +13266,20 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M130" s="7" t="n">
+      <c r="M130" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
@@ -13287,7 +13287,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O130" s="8" t="inlineStr">
+      <c r="O130" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13376,7 +13376,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M131" s="7" t="n">
+      <c r="M131" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N131" s="4" t="inlineStr">
@@ -13384,7 +13384,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O131" s="8" t="inlineStr">
+      <c r="O131" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13460,20 +13460,20 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M132" s="7" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M132" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
@@ -13481,7 +13481,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O132" s="8" t="inlineStr">
+      <c r="O132" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13505,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,37 +13557,37 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K133" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M133" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="L133" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M133" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N133" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O133" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -13654,20 +13654,20 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M134" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M134" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
@@ -13675,7 +13675,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O134" s="8" t="inlineStr">
+      <c r="O134" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13751,20 +13751,20 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M135" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M135" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
@@ -13772,7 +13772,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O135" s="8" t="inlineStr">
+      <c r="O135" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13848,20 +13848,20 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M136" s="7" t="n">
+        <v>-27</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M136" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
@@ -13869,7 +13869,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O136" s="8" t="inlineStr">
+      <c r="O136" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13945,20 +13945,20 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M137" s="7" t="n">
+      <c r="M137" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
@@ -13966,7 +13966,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O137" s="8" t="inlineStr">
+      <c r="O137" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,20 +14042,20 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L138" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M138" s="7" t="n">
+      <c r="M138" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
@@ -14063,7 +14063,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O138" s="8" t="inlineStr">
+      <c r="O138" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14086,11 +14086,11 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>3</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X138" s="10" t="n">
         <v>7</v>
@@ -14139,20 +14139,20 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M139" s="7" t="n">
+      <c r="M139" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
@@ -14160,7 +14160,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O139" s="8" t="inlineStr">
+      <c r="O139" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14236,20 +14236,20 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M140" s="7" t="n">
+        <v>-34</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M140" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
@@ -14257,7 +14257,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O140" s="8" t="inlineStr">
+      <c r="O140" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14346,7 +14346,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M141" s="7" t="n">
+      <c r="M141" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N141" s="4" t="inlineStr">
@@ -14354,7 +14354,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O141" s="8" t="inlineStr">
+      <c r="O141" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14430,20 +14430,20 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L142" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M142" s="7" t="n">
+      <c r="M142" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
@@ -14451,7 +14451,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O142" s="8" t="inlineStr">
+      <c r="O142" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14527,20 +14527,20 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M143" s="7" t="n">
+      <c r="M143" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
@@ -14548,7 +14548,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O143" s="8" t="inlineStr">
+      <c r="O143" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14575,7 +14575,7 @@
         <v>4</v>
       </c>
       <c r="W143" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X143" s="10" t="n">
         <v>6</v>
@@ -14624,20 +14624,20 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M144" s="7" t="n">
+      <c r="M144" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N144" s="4" t="inlineStr">
@@ -14645,7 +14645,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O144" s="8" t="inlineStr">
+      <c r="O144" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14721,20 +14721,20 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M145" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M145" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
@@ -14742,7 +14742,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O145" s="8" t="inlineStr">
+      <c r="O145" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14818,20 +14818,20 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M146" s="7" t="n">
+      <c r="M146" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
@@ -14839,7 +14839,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O146" s="8" t="inlineStr">
+      <c r="O146" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14915,20 +14915,20 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M147" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M147" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N147" s="4" t="inlineStr">
@@ -14936,7 +14936,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O147" s="8" t="inlineStr">
+      <c r="O147" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14998,7 +14998,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15012,20 +15012,20 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M148" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M148" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N148" s="4" t="inlineStr">
@@ -15033,7 +15033,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O148" s="8" t="inlineStr">
+      <c r="O148" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15056,11 +15056,11 @@
       <c r="U148" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W148" s="9" t="n">
-        <v>0</v>
+      <c r="V148" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W148" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X148" s="10" t="n">
         <v>6</v>
@@ -15109,20 +15109,20 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M149" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M149" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N149" s="4" t="inlineStr">
@@ -15130,7 +15130,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O149" s="8" t="inlineStr">
+      <c r="O149" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15206,20 +15206,20 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M150" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L150" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M150" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N150" s="4" t="inlineStr">
@@ -15227,7 +15227,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O150" s="8" t="inlineStr">
+      <c r="O150" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15303,20 +15303,20 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L151" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M151" s="7" t="n">
+      <c r="M151" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N151" s="4" t="inlineStr">
@@ -15324,7 +15324,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O151" s="8" t="inlineStr">
+      <c r="O151" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15400,20 +15400,20 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M152" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L152" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M152" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N152" s="4" t="inlineStr">
@@ -15421,7 +15421,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O152" s="8" t="inlineStr">
+      <c r="O152" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15497,20 +15497,20 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L153" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M153" s="7" t="n">
+      <c r="M153" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N153" s="4" t="inlineStr">
@@ -15518,7 +15518,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O153" s="8" t="inlineStr">
+      <c r="O153" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15594,20 +15594,20 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M154" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M154" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N154" s="4" t="inlineStr">
@@ -15615,13 +15615,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O154" s="8" t="inlineStr">
+      <c r="O154" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q154" s="9" t="n">
         <v>0</v>
@@ -15629,8 +15629,8 @@
       <c r="R154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S154" s="9" t="n">
-        <v>0</v>
+      <c r="S154" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T154" s="9" t="n">
         <v>0</v>
@@ -15691,20 +15691,20 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L155" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L155" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M155" s="7" t="n">
+      <c r="M155" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
@@ -15712,7 +15712,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O155" s="8" t="inlineStr">
+      <c r="O155" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15788,20 +15788,20 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M156" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L156" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M156" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N156" s="4" t="inlineStr">
@@ -15809,7 +15809,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O156" s="8" t="inlineStr">
+      <c r="O156" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15885,20 +15885,20 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M157" s="7" t="n">
+      <c r="M157" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N157" s="4" t="inlineStr">
@@ -15906,7 +15906,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O157" s="8" t="inlineStr">
+      <c r="O157" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15929,11 +15929,11 @@
       <c r="U157" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="V157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W157" s="9" t="n">
-        <v>0</v>
+      <c r="V157" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W157" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="X157" s="10" t="n">
         <v>7</v>
@@ -15982,20 +15982,20 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M158" s="7" t="n">
+      <c r="M158" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N158" s="4" t="inlineStr">
@@ -16003,7 +16003,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O158" s="8" t="inlineStr">
+      <c r="O158" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16030,7 +16030,7 @@
         <v>4</v>
       </c>
       <c r="W158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X158" s="10" t="n">
         <v>7</v>
@@ -16079,20 +16079,20 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M159" s="7" t="n">
+      <c r="M159" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N159" s="4" t="inlineStr">
@@ -16100,7 +16100,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O159" s="8" t="inlineStr">
+      <c r="O159" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16176,20 +16176,20 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L160" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M160" s="7" t="n">
+      <c r="M160" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N160" s="4" t="inlineStr">
@@ -16197,7 +16197,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O160" s="8" t="inlineStr">
+      <c r="O160" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16273,20 +16273,20 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L161" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L161" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M161" s="7" t="n">
+      <c r="M161" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N161" s="4" t="inlineStr">
@@ -16294,7 +16294,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O161" s="8" t="inlineStr">
+      <c r="O161" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16439,7 +16439,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -16457,7 +16457,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16490,7 +16490,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16523,13 +16523,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -16571,7 +16571,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -16589,7 +16589,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16604,7 +16604,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -16622,7 +16622,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16637,7 +16637,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -16655,7 +16655,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -16670,7 +16670,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -16688,7 +16688,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -16736,7 +16736,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -16754,7 +16754,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16802,7 +16802,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -16820,7 +16820,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -16868,7 +16868,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -16886,7 +16886,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -16934,7 +16934,7 @@
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -16985,7 +16985,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -17000,7 +17000,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -17018,7 +17018,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17033,7 +17033,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -17051,7 +17051,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17066,7 +17066,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -17084,7 +17084,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -17099,7 +17099,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -17117,13 +17117,13 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -17150,13 +17150,13 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -17183,7 +17183,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -17198,7 +17198,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -17231,7 +17231,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -17249,13 +17249,13 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -17282,7 +17282,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -17348,7 +17348,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -17381,7 +17381,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -17396,7 +17396,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -17429,7 +17429,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -17447,13 +17447,13 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -17462,7 +17462,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -17480,7 +17480,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -17495,7 +17495,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">

--- a/docs/d/229/inyear.xlsx
+++ b/docs/d/229/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/229/inyear.xlsx
+++ b/docs/d/229/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/229/inyear.xlsx
+++ b/docs/d/229/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/229/inyear.xlsx
+++ b/docs/d/229/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/229/inyear.xlsx
+++ b/docs/d/229/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1670,11 +1670,11 @@
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W10" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>7</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>2</v>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="9" t="n">
         <v>1</v>
@@ -1867,8 +1867,8 @@
       <c r="V12" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W12" s="9" t="n">
-        <v>1</v>
+      <c r="W12" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X12" s="10" t="n">
         <v>7</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -1961,8 +1961,8 @@
       <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="9" t="n">
-        <v>3</v>
+      <c r="V13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2887,17 +2887,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -2931,11 +2931,11 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>0</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3954,17 +3954,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="9" t="n">
         <v>0</v>
@@ -3998,11 +3998,11 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="9" t="n">
-        <v>0</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W34" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>7</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5059,14 +5059,14 @@
       <c r="S45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T45" s="9" t="n">
-        <v>0</v>
+      <c r="T45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>1</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5353,8 +5353,8 @@
       <c r="T48" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U48" s="9" t="n">
-        <v>0</v>
+      <c r="U48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V48" s="10" t="n">
         <v>4</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>7</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5641,8 +5641,8 @@
       <c r="S51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T51" s="9" t="n">
-        <v>0</v>
+      <c r="T51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U51" s="9" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5894,17 +5894,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-38</v>
-      </c>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -5938,11 +5938,11 @@
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="9" t="n">
-        <v>0</v>
+      <c r="V54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>4</v>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6035,8 +6035,8 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>2</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6476,17 +6476,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6524,7 +6524,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>7</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8939,8 +8939,8 @@
       <c r="S85" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9121,11 +9121,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P87" s="9" t="n">
-        <v>3</v>
+      <c r="P87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>0</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9221,8 +9221,8 @@
       <c r="P88" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q88" s="9" t="n">
-        <v>1</v>
+      <c r="Q88" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10094,8 +10094,8 @@
       <c r="P97" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q97" s="9" t="n">
-        <v>1</v>
+      <c r="Q97" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>1</v>
       </c>
       <c r="U105" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V105" s="10" t="n">
         <v>4</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11467,11 +11467,11 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>3</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>7</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L112" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -11564,11 +11564,11 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" s="9" t="n">
-        <v>0</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W112" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X112" s="10" t="n">
         <v>6</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11643,8 +11643,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P113" s="9" t="n">
-        <v>3</v>
+      <c r="P113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -11952,11 +11952,11 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>2</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X116" s="10" t="n">
         <v>7</v>
@@ -12226,7 +12226,7 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -12713,8 +12713,8 @@
       <c r="P124" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q124" s="9" t="n">
-        <v>1</v>
+      <c r="Q124" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R124" s="9" t="n">
         <v>0</v>
@@ -12732,7 +12732,7 @@
         <v>4</v>
       </c>
       <c r="W124" s="10" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>7</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-18</v>
+        <v>-9</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,17 +14236,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-34</v>
-      </c>
-      <c r="L140" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -14280,11 +14280,11 @@
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" s="9" t="n">
-        <v>0</v>
+      <c r="V140" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W140" s="10" t="n">
+        <v>24</v>
       </c>
       <c r="X140" s="9" t="n">
         <v>1</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -14765,8 +14765,8 @@
       <c r="U145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V145" s="9" t="n">
-        <v>0</v>
+      <c r="V145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14956,8 +14956,8 @@
       <c r="T147" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U147" s="9" t="n">
-        <v>0</v>
+      <c r="U147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V147" s="9" t="n">
         <v>0</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>4</v>
       </c>
       <c r="W148" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X148" s="10" t="n">
         <v>6</v>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>6</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L150" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M150" s="8" t="n">
@@ -15251,7 +15251,7 @@
         <v>9</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15524,7 +15524,7 @@
         </is>
       </c>
       <c r="P153" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q153" s="9" t="n">
         <v>0</v>
@@ -15532,8 +15532,8 @@
       <c r="R153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S153" s="9" t="n">
-        <v>1</v>
+      <c r="S153" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T153" s="9" t="n">
         <v>0</v>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q157" s="10" t="n">
         <v>2</v>
@@ -15920,8 +15920,8 @@
       <c r="R157" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S157" s="9" t="n">
-        <v>1</v>
+      <c r="S157" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T157" s="10" t="n">
         <v>1</v>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
@@ -16105,14 +16105,14 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P159" s="9" t="n">
-        <v>3</v>
+      <c r="P159" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q159" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S159" s="10" t="n">
         <v>2</v>
@@ -16126,8 +16126,8 @@
       <c r="V159" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W159" s="9" t="n">
-        <v>3</v>
+      <c r="W159" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X159" s="10" t="n">
         <v>7</v>
@@ -16457,7 +16457,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16490,13 +16490,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16571,7 +16571,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -16622,7 +16622,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16637,7 +16637,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -16721,7 +16721,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16769,7 +16769,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -16787,7 +16787,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -16835,7 +16835,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -16985,7 +16985,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -17018,13 +17018,13 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -17084,13 +17084,13 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -17183,7 +17183,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -17198,7 +17198,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -17216,7 +17216,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -17282,7 +17282,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17381,7 +17381,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -17396,7 +17396,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -17414,7 +17414,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -17462,7 +17462,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -17480,7 +17480,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -17513,7 +17513,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>

--- a/docs/d/229/inyear.xlsx
+++ b/docs/d/229/inyear.xlsx
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -850,20 +850,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-26</v>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M2" s="8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -871,7 +871,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -894,8 +894,8 @@
       <c r="U2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="9" t="n">
-        <v>0</v>
+      <c r="V2" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -955,12 +955,12 @@
       <c r="K3" s="4" t="n">
         <v>-11</v>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -968,7 +968,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1052,12 +1052,12 @@
       <c r="K4" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1065,7 +1065,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1149,12 +1149,12 @@
       <c r="K5" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1162,7 +1162,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1251,7 +1251,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1259,7 +1259,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1267,8 +1267,8 @@
       <c r="P6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" s="9" t="n">
-        <v>0</v>
+      <c r="Q6" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R6" s="9" t="n">
         <v>0</v>
@@ -1338,17 +1338,17 @@
         <v>23</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1356,7 +1356,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1432,20 +1432,20 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1453,7 +1453,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="O8" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1476,8 +1476,8 @@
       <c r="U8" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="9" t="n">
-        <v>3</v>
+      <c r="V8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1542,7 +1542,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1550,7 +1550,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="O9" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1626,20 +1626,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="O10" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1673,8 +1673,8 @@
       <c r="V10" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W10" s="9" t="n">
-        <v>3</v>
+      <c r="W10" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>7</v>
@@ -1736,7 +1736,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1744,7 +1744,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="O11" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1833,7 +1833,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1841,7 +1841,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1938,16 +1938,16 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P13" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="9" t="n">
-        <v>1</v>
+      <c r="P13" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>0</v>
@@ -1955,8 +1955,8 @@
       <c r="S13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T13" s="9" t="n">
-        <v>0</v>
+      <c r="T13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U13" s="9" t="n">
         <v>0</v>
@@ -2014,20 +2014,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2035,7 +2035,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2119,12 +2119,12 @@
       <c r="K15" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2132,7 +2132,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2152,8 +2152,8 @@
       <c r="T15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U15" s="9" t="n">
-        <v>0</v>
+      <c r="U15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2229,13 +2229,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>1</v>
@@ -2318,7 +2318,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2326,7 +2326,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2402,20 +2402,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2423,7 +2423,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2512,7 +2512,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2520,7 +2520,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2604,12 +2604,12 @@
       <c r="K20" s="4" t="n">
         <v>-21</v>
       </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2617,7 +2617,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2701,12 +2701,12 @@
       <c r="K21" s="4" t="n">
         <v>-9</v>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2714,7 +2714,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="O21" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2790,20 +2790,20 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-26</v>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2811,7 +2811,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="O22" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2834,8 +2834,8 @@
       <c r="U22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V22" s="9" t="n">
-        <v>0</v>
+      <c r="V22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -2900,7 +2900,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M23" s="8" t="n">
+      <c r="M23" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2908,13 +2908,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="O23" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P23" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -2997,7 +2997,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -3005,7 +3005,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="O24" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3089,12 +3089,12 @@
       <c r="K25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="7" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -3102,7 +3102,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3186,12 +3186,12 @@
       <c r="K26" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L26" s="7" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3199,7 +3199,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
+      <c r="O26" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3283,12 +3283,12 @@
       <c r="K27" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3296,7 +3296,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
+      <c r="O27" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3385,7 +3385,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3393,7 +3393,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr">
+      <c r="O28" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3482,7 +3482,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3490,7 +3490,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
+      <c r="O29" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3574,12 +3574,12 @@
       <c r="K30" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="M30" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3587,19 +3587,19 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="O30" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R30" s="9" t="n">
-        <v>1</v>
+      <c r="R30" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S30" s="10" t="n">
         <v>2</v>
@@ -3671,12 +3671,12 @@
       <c r="K31" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3684,7 +3684,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="7" t="inlineStr">
+      <c r="O31" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3773,7 +3773,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3781,7 +3781,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="7" t="inlineStr">
+      <c r="O32" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3857,20 +3857,20 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -3878,7 +3878,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="7" t="inlineStr">
+      <c r="O33" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -3975,7 +3975,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O34" s="7" t="inlineStr">
+      <c r="O34" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4051,20 +4051,20 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4072,13 +4072,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O35" s="7" t="inlineStr">
+      <c r="O35" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="10" t="n">
         <v>2</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" s="10" t="n">
         <v>1</v>
@@ -4099,7 +4099,7 @@
         <v>4</v>
       </c>
       <c r="W35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>7</v>
@@ -4148,20 +4148,20 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4169,7 +4169,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O36" s="7" t="inlineStr">
+      <c r="O36" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4253,12 +4253,12 @@
       <c r="K37" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="L37" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M37" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4266,7 +4266,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="7" t="inlineStr">
+      <c r="O37" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4350,12 +4350,12 @@
       <c r="K38" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="L38" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4363,7 +4363,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="7" t="inlineStr">
+      <c r="O38" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4447,12 +4447,12 @@
       <c r="K39" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="L39" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4460,7 +4460,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="7" t="inlineStr">
+      <c r="O39" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4549,7 +4549,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4557,7 +4557,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="7" t="inlineStr">
+      <c r="O40" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4646,7 +4646,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="M41" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4654,7 +4654,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="7" t="inlineStr">
+      <c r="O41" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4743,7 +4743,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -4751,7 +4751,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O42" s="7" t="inlineStr">
+      <c r="O42" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4840,7 +4840,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M43" s="8" t="n">
+      <c r="M43" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -4848,7 +4848,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="7" t="inlineStr">
+      <c r="O43" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4932,12 +4932,12 @@
       <c r="K44" s="4" t="n">
         <v>-11</v>
       </c>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="L44" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M44" s="8" t="n">
+      <c r="M44" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -4945,7 +4945,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O44" s="7" t="inlineStr">
+      <c r="O44" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5029,12 +5029,12 @@
       <c r="K45" s="4" t="n">
         <v>-13</v>
       </c>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="L45" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M45" s="8" t="n">
+      <c r="M45" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5042,7 +5042,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="7" t="inlineStr">
+      <c r="O45" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5050,14 +5050,14 @@
       <c r="P45" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="9" t="n">
-        <v>1</v>
+      <c r="Q45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S45" s="9" t="n">
-        <v>1</v>
+      <c r="S45" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T45" s="10" t="n">
         <v>1</v>
@@ -5126,12 +5126,12 @@
       <c r="K46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="L46" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="7" t="n">
         <v>46387</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5139,7 +5139,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O46" s="7" t="inlineStr">
+      <c r="O46" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5228,7 +5228,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M47" s="8" t="n">
+      <c r="M47" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5236,7 +5236,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O47" s="7" t="inlineStr">
+      <c r="O47" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5325,7 +5325,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M48" s="8" t="n">
+      <c r="M48" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5333,13 +5333,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="7" t="inlineStr">
+      <c r="O48" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -5417,12 +5417,12 @@
       <c r="K49" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="L49" s="7" t="inlineStr">
+      <c r="L49" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M49" s="8" t="n">
+      <c r="M49" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5430,7 +5430,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O49" s="7" t="inlineStr">
+      <c r="O49" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5519,7 +5519,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M50" s="8" t="n">
+      <c r="M50" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5527,13 +5527,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O50" s="7" t="inlineStr">
+      <c r="O50" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q50" s="9" t="n">
         <v>0</v>
@@ -5616,7 +5616,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M51" s="8" t="n">
+      <c r="M51" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5624,7 +5624,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O51" s="7" t="inlineStr">
+      <c r="O51" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5713,7 +5713,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M52" s="8" t="n">
+      <c r="M52" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5721,7 +5721,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="7" t="inlineStr">
+      <c r="O52" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5805,12 +5805,12 @@
       <c r="K53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L53" s="7" t="inlineStr">
+      <c r="L53" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M53" s="8" t="n">
+      <c r="M53" s="7" t="n">
         <v>46387</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5818,7 +5818,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O53" s="7" t="inlineStr">
+      <c r="O53" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5907,7 +5907,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M54" s="8" t="n">
+      <c r="M54" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -5915,7 +5915,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="7" t="inlineStr">
+      <c r="O54" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5999,12 +5999,12 @@
       <c r="K55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L55" s="7" t="inlineStr">
+      <c r="L55" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M55" s="8" t="n">
+      <c r="M55" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6012,7 +6012,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="7" t="inlineStr">
+      <c r="O55" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6101,7 +6101,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M56" s="8" t="n">
+      <c r="M56" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6109,7 +6109,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="7" t="inlineStr">
+      <c r="O56" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6198,7 +6198,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M57" s="8" t="n">
+      <c r="M57" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6206,7 +6206,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O57" s="7" t="inlineStr">
+      <c r="O57" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6290,12 +6290,12 @@
       <c r="K58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L58" s="7" t="inlineStr">
+      <c r="L58" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M58" s="8" t="n">
+      <c r="M58" s="7" t="n">
         <v>46387</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -6303,7 +6303,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O58" s="7" t="inlineStr">
+      <c r="O58" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6387,12 +6387,12 @@
       <c r="K59" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L59" s="7" t="inlineStr">
+      <c r="L59" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M59" s="8" t="n">
+      <c r="M59" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6400,7 +6400,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O59" s="7" t="inlineStr">
+      <c r="O59" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6489,7 +6489,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M60" s="8" t="n">
+      <c r="M60" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6497,7 +6497,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O60" s="7" t="inlineStr">
+      <c r="O60" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6514,8 +6514,8 @@
       <c r="S60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T60" s="9" t="n">
-        <v>0</v>
+      <c r="T60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U60" s="9" t="n">
         <v>0</v>
@@ -6586,7 +6586,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M61" s="8" t="n">
+      <c r="M61" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6594,7 +6594,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O61" s="7" t="inlineStr">
+      <c r="O61" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6615,7 +6615,7 @@
         <v>1</v>
       </c>
       <c r="U61" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V61" s="10" t="n">
         <v>4</v>
@@ -6683,7 +6683,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M62" s="8" t="n">
+      <c r="M62" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -6691,7 +6691,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="7" t="inlineStr">
+      <c r="O62" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6780,7 +6780,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M63" s="8" t="n">
+      <c r="M63" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -6788,7 +6788,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O63" s="7" t="inlineStr">
+      <c r="O63" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6803,13 +6803,13 @@
         <v>0</v>
       </c>
       <c r="S63" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="T63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V63" s="10" t="n">
         <v>4</v>
@@ -6877,7 +6877,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M64" s="8" t="n">
+      <c r="M64" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -6885,7 +6885,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="7" t="inlineStr">
+      <c r="O64" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6969,12 +6969,12 @@
       <c r="K65" s="4" t="n">
         <v>-7</v>
       </c>
-      <c r="L65" s="7" t="inlineStr">
+      <c r="L65" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M65" s="8" t="n">
+      <c r="M65" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -6982,7 +6982,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O65" s="7" t="inlineStr">
+      <c r="O65" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7071,7 +7071,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M66" s="8" t="n">
+      <c r="M66" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7079,7 +7079,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O66" s="7" t="inlineStr">
+      <c r="O66" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7163,12 +7163,12 @@
       <c r="K67" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="L67" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M67" s="8" t="n">
+      <c r="M67" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -7176,7 +7176,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O67" s="7" t="inlineStr">
+      <c r="O67" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7260,12 +7260,12 @@
       <c r="K68" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="L68" s="7" t="inlineStr">
+      <c r="L68" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M68" s="8" t="n">
+      <c r="M68" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7273,7 +7273,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="7" t="inlineStr">
+      <c r="O68" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7357,12 +7357,12 @@
       <c r="K69" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L69" s="7" t="inlineStr">
+      <c r="L69" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M69" s="8" t="n">
+      <c r="M69" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7370,7 +7370,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O69" s="7" t="inlineStr">
+      <c r="O69" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7454,12 +7454,12 @@
       <c r="K70" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="L70" s="7" t="inlineStr">
+      <c r="L70" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M70" s="8" t="n">
+      <c r="M70" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7467,7 +7467,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O70" s="7" t="inlineStr">
+      <c r="O70" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7551,12 +7551,12 @@
       <c r="K71" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="L71" s="7" t="inlineStr">
+      <c r="L71" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M71" s="8" t="n">
+      <c r="M71" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -7564,7 +7564,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O71" s="7" t="inlineStr">
+      <c r="O71" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7648,12 +7648,12 @@
       <c r="K72" s="4" t="n">
         <v>-18</v>
       </c>
-      <c r="L72" s="7" t="inlineStr">
+      <c r="L72" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M72" s="8" t="n">
+      <c r="M72" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -7661,7 +7661,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O72" s="7" t="inlineStr">
+      <c r="O72" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7750,7 +7750,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M73" s="8" t="n">
+      <c r="M73" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -7758,7 +7758,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O73" s="7" t="inlineStr">
+      <c r="O73" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7842,12 +7842,12 @@
       <c r="K74" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="L74" s="7" t="inlineStr">
+      <c r="L74" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M74" s="8" t="n">
+      <c r="M74" s="7" t="n">
         <v>46387</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -7855,7 +7855,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O74" s="7" t="inlineStr">
+      <c r="O74" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7939,12 +7939,12 @@
       <c r="K75" s="4" t="n">
         <v>-15</v>
       </c>
-      <c r="L75" s="7" t="inlineStr">
+      <c r="L75" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M75" s="8" t="n">
+      <c r="M75" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -7952,7 +7952,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O75" s="7" t="inlineStr">
+      <c r="O75" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8036,12 +8036,12 @@
       <c r="K76" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="L76" s="7" t="inlineStr">
+      <c r="L76" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M76" s="8" t="n">
+      <c r="M76" s="7" t="n">
         <v>46387</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8049,7 +8049,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O76" s="7" t="inlineStr">
+      <c r="O76" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8133,12 +8133,12 @@
       <c r="K77" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="L77" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M77" s="8" t="n">
+      <c r="M77" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8146,7 +8146,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O77" s="7" t="inlineStr">
+      <c r="O77" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8235,7 +8235,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M78" s="8" t="n">
+      <c r="M78" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8243,7 +8243,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="7" t="inlineStr">
+      <c r="O78" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8332,7 +8332,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M79" s="8" t="n">
+      <c r="M79" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8340,7 +8340,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O79" s="7" t="inlineStr">
+      <c r="O79" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8416,20 +8416,20 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L80" s="7" t="inlineStr">
+        <v>-13</v>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M80" s="8" t="n">
+      <c r="M80" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8437,7 +8437,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O80" s="7" t="inlineStr">
+      <c r="O80" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8461,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8526,7 +8526,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M81" s="8" t="n">
+      <c r="M81" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -8534,7 +8534,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O81" s="7" t="inlineStr">
+      <c r="O81" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8618,12 +8618,12 @@
       <c r="K82" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L82" s="7" t="inlineStr">
+      <c r="L82" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M82" s="8" t="n">
+      <c r="M82" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -8631,7 +8631,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="7" t="inlineStr">
+      <c r="O82" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8720,7 +8720,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M83" s="8" t="n">
+      <c r="M83" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -8728,7 +8728,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="7" t="inlineStr">
+      <c r="O83" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8812,12 +8812,12 @@
       <c r="K84" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="L84" s="7" t="inlineStr">
+      <c r="L84" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M84" s="8" t="n">
+      <c r="M84" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -8825,7 +8825,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O84" s="7" t="inlineStr">
+      <c r="O84" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8914,7 +8914,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M85" s="8" t="n">
+      <c r="M85" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -8922,7 +8922,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="7" t="inlineStr">
+      <c r="O85" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9006,12 +9006,12 @@
       <c r="K86" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="L86" s="7" t="inlineStr">
+      <c r="L86" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M86" s="8" t="n">
+      <c r="M86" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9019,7 +9019,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="7" t="inlineStr">
+      <c r="O86" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9108,7 +9108,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M87" s="8" t="n">
+      <c r="M87" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9116,7 +9116,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O87" s="7" t="inlineStr">
+      <c r="O87" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9200,12 +9200,12 @@
       <c r="K88" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="L88" s="7" t="inlineStr">
+      <c r="L88" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M88" s="8" t="n">
+      <c r="M88" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -9213,7 +9213,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O88" s="7" t="inlineStr">
+      <c r="O88" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9297,12 +9297,12 @@
       <c r="K89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L89" s="7" t="inlineStr">
+      <c r="L89" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M89" s="8" t="n">
+      <c r="M89" s="7" t="n">
         <v>46387</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9310,7 +9310,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O89" s="7" t="inlineStr">
+      <c r="O89" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9394,12 +9394,12 @@
       <c r="K90" s="4" t="n">
         <v>-13</v>
       </c>
-      <c r="L90" s="7" t="inlineStr">
+      <c r="L90" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M90" s="8" t="n">
+      <c r="M90" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9407,7 +9407,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O90" s="7" t="inlineStr">
+      <c r="O90" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9496,7 +9496,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M91" s="8" t="n">
+      <c r="M91" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -9504,7 +9504,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O91" s="7" t="inlineStr">
+      <c r="O91" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9580,20 +9580,20 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L92" s="7" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L92" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M92" s="8" t="n">
+      <c r="M92" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -9601,7 +9601,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="7" t="inlineStr">
+      <c r="O92" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -9685,12 +9685,12 @@
       <c r="K93" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="L93" s="7" t="inlineStr">
+      <c r="L93" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M93" s="8" t="n">
+      <c r="M93" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -9698,7 +9698,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="7" t="inlineStr">
+      <c r="O93" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9782,12 +9782,12 @@
       <c r="K94" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L94" s="7" t="inlineStr">
+      <c r="L94" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M94" s="8" t="n">
+      <c r="M94" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -9795,7 +9795,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="7" t="inlineStr">
+      <c r="O94" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9871,20 +9871,20 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-33</v>
-      </c>
-      <c r="L95" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M95" s="8" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -9892,7 +9892,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O95" s="7" t="inlineStr">
+      <c r="O95" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9906,20 +9906,20 @@
       <c r="R95" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S95" s="9" t="n">
-        <v>1</v>
+      <c r="S95" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T95" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V95" s="9" t="n">
-        <v>0</v>
+      <c r="U95" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>7</v>
@@ -9976,12 +9976,12 @@
       <c r="K96" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L96" s="7" t="inlineStr">
+      <c r="L96" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M96" s="8" t="n">
+      <c r="M96" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -9989,7 +9989,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O96" s="7" t="inlineStr">
+      <c r="O96" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10078,7 +10078,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M97" s="8" t="n">
+      <c r="M97" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10086,7 +10086,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="7" t="inlineStr">
+      <c r="O97" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10175,7 +10175,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M98" s="8" t="n">
+      <c r="M98" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10183,7 +10183,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O98" s="7" t="inlineStr">
+      <c r="O98" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10267,12 +10267,12 @@
       <c r="K99" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="L99" s="7" t="inlineStr">
+      <c r="L99" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M99" s="8" t="n">
+      <c r="M99" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10280,7 +10280,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O99" s="7" t="inlineStr">
+      <c r="O99" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10289,7 +10289,7 @@
         <v>1</v>
       </c>
       <c r="Q99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" s="9" t="n">
         <v>0</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10364,12 +10364,12 @@
       <c r="K100" s="4" t="n">
         <v>-11</v>
       </c>
-      <c r="L100" s="7" t="inlineStr">
+      <c r="L100" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M100" s="8" t="n">
+      <c r="M100" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -10377,7 +10377,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O100" s="7" t="inlineStr">
+      <c r="O100" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10391,8 +10391,8 @@
       <c r="R100" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="S100" s="9" t="n">
-        <v>1</v>
+      <c r="S100" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T100" s="10" t="n">
         <v>1</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10466,7 +10466,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M101" s="8" t="n">
+      <c r="M101" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -10474,13 +10474,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O101" s="7" t="inlineStr">
+      <c r="O101" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P101" s="9" t="n">
-        <v>3</v>
+      <c r="P101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q101" s="10" t="n">
         <v>2</v>
@@ -10558,12 +10558,12 @@
       <c r="K102" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="L102" s="7" t="inlineStr">
+      <c r="L102" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M102" s="8" t="n">
+      <c r="M102" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -10571,7 +10571,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O102" s="7" t="inlineStr">
+      <c r="O102" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10660,7 +10660,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M103" s="8" t="n">
+      <c r="M103" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -10668,7 +10668,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O103" s="7" t="inlineStr">
+      <c r="O103" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10757,7 +10757,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M104" s="8" t="n">
+      <c r="M104" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -10765,13 +10765,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O104" s="7" t="inlineStr">
+      <c r="O104" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P104" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -10854,7 +10854,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M105" s="8" t="n">
+      <c r="M105" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -10862,7 +10862,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O105" s="7" t="inlineStr">
+      <c r="O105" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10946,12 +10946,12 @@
       <c r="K106" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L106" s="7" t="inlineStr">
+      <c r="L106" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M106" s="8" t="n">
+      <c r="M106" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -10959,7 +10959,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O106" s="7" t="inlineStr">
+      <c r="O106" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11048,7 +11048,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M107" s="8" t="n">
+      <c r="M107" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -11056,7 +11056,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O107" s="7" t="inlineStr">
+      <c r="O107" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11145,7 +11145,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M108" s="8" t="n">
+      <c r="M108" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -11153,13 +11153,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O108" s="7" t="inlineStr">
+      <c r="O108" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P108" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11242,7 +11242,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M109" s="8" t="n">
+      <c r="M109" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
@@ -11250,7 +11250,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O109" s="7" t="inlineStr">
+      <c r="O109" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11339,7 +11339,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M110" s="8" t="n">
+      <c r="M110" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
@@ -11347,7 +11347,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O110" s="7" t="inlineStr">
+      <c r="O110" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11423,20 +11423,20 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M111" s="8" t="n">
+      <c r="M111" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -11444,13 +11444,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O111" s="7" t="inlineStr">
+      <c r="O111" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>1</v>
@@ -11471,7 +11471,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>7</v>
@@ -11533,7 +11533,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M112" s="8" t="n">
+      <c r="M112" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
@@ -11541,7 +11541,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O112" s="7" t="inlineStr">
+      <c r="O112" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11630,7 +11630,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M113" s="8" t="n">
+      <c r="M113" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -11638,7 +11638,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O113" s="7" t="inlineStr">
+      <c r="O113" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11647,7 +11647,7 @@
         <v>4</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M114" s="8" t="n">
+      <c r="M114" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -11735,7 +11735,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O114" s="7" t="inlineStr">
+      <c r="O114" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11824,7 +11824,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M115" s="8" t="n">
+      <c r="M115" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -11832,7 +11832,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O115" s="7" t="inlineStr">
+      <c r="O115" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11916,12 +11916,12 @@
       <c r="K116" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="L116" s="7" t="inlineStr">
+      <c r="L116" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M116" s="8" t="n">
+      <c r="M116" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -11929,7 +11929,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O116" s="7" t="inlineStr">
+      <c r="O116" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12013,12 +12013,12 @@
       <c r="K117" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L117" s="7" t="inlineStr">
+      <c r="L117" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M117" s="8" t="n">
+      <c r="M117" s="7" t="n">
         <v>46387</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -12026,7 +12026,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O117" s="7" t="inlineStr">
+      <c r="O117" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12115,7 +12115,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M118" s="8" t="n">
+      <c r="M118" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
@@ -12123,7 +12123,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O118" s="7" t="inlineStr">
+      <c r="O118" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12212,7 +12212,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M119" s="8" t="n">
+      <c r="M119" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -12220,13 +12220,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O119" s="7" t="inlineStr">
+      <c r="O119" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -12234,8 +12234,8 @@
       <c r="R119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S119" s="9" t="n">
-        <v>1</v>
+      <c r="S119" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T119" s="10" t="n">
         <v>1</v>
@@ -12309,7 +12309,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M120" s="8" t="n">
+      <c r="M120" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
@@ -12317,13 +12317,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O120" s="7" t="inlineStr">
+      <c r="O120" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q120" s="9" t="n">
         <v>0</v>
@@ -12406,7 +12406,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M121" s="8" t="n">
+      <c r="M121" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -12414,7 +12414,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O121" s="7" t="inlineStr">
+      <c r="O121" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12498,12 +12498,12 @@
       <c r="K122" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L122" s="7" t="inlineStr">
+      <c r="L122" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M122" s="8" t="n">
+      <c r="M122" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -12511,13 +12511,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O122" s="7" t="inlineStr">
+      <c r="O122" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P122" s="9" t="n">
-        <v>3</v>
+      <c r="P122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -12526,7 +12526,7 @@
         <v>0</v>
       </c>
       <c r="S122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T122" s="10" t="n">
         <v>1</v>
@@ -12595,12 +12595,12 @@
       <c r="K123" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L123" s="7" t="inlineStr">
+      <c r="L123" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M123" s="8" t="n">
+      <c r="M123" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -12608,7 +12608,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O123" s="7" t="inlineStr">
+      <c r="O123" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12697,7 +12697,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M124" s="8" t="n">
+      <c r="M124" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -12705,7 +12705,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O124" s="7" t="inlineStr">
+      <c r="O124" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12789,12 +12789,12 @@
       <c r="K125" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L125" s="7" t="inlineStr">
+      <c r="L125" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M125" s="8" t="n">
+      <c r="M125" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -12802,7 +12802,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O125" s="7" t="inlineStr">
+      <c r="O125" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12886,12 +12886,12 @@
       <c r="K126" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L126" s="7" t="inlineStr">
+      <c r="L126" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M126" s="8" t="n">
+      <c r="M126" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
@@ -12899,7 +12899,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O126" s="7" t="inlineStr">
+      <c r="O126" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -12975,20 +12975,20 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L127" s="7" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L127" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M127" s="8" t="n">
+      <c r="M127" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
@@ -12996,7 +12996,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O127" s="7" t="inlineStr">
+      <c r="O127" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13019,8 +13019,8 @@
       <c r="U127" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>2</v>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13080,12 +13080,12 @@
       <c r="K128" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L128" s="7" t="inlineStr">
+      <c r="L128" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M128" s="8" t="n">
+      <c r="M128" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N128" s="4" t="inlineStr">
@@ -13093,7 +13093,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O128" s="7" t="inlineStr">
+      <c r="O128" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13177,12 +13177,12 @@
       <c r="K129" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="L129" s="7" t="inlineStr">
+      <c r="L129" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M129" s="8" t="n">
+      <c r="M129" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
@@ -13190,7 +13190,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O129" s="7" t="inlineStr">
+      <c r="O129" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13279,7 +13279,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M130" s="8" t="n">
+      <c r="M130" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
@@ -13287,7 +13287,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O130" s="7" t="inlineStr">
+      <c r="O130" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13376,7 +13376,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M131" s="8" t="n">
+      <c r="M131" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N131" s="4" t="inlineStr">
@@ -13384,7 +13384,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O131" s="7" t="inlineStr">
+      <c r="O131" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13468,12 +13468,12 @@
       <c r="K132" s="4" t="n">
         <v>-12</v>
       </c>
-      <c r="L132" s="7" t="inlineStr">
+      <c r="L132" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M132" s="8" t="n">
+      <c r="M132" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
@@ -13481,7 +13481,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O132" s="7" t="inlineStr">
+      <c r="O132" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13565,12 +13565,12 @@
       <c r="K133" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="L133" s="7" t="inlineStr">
+      <c r="L133" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M133" s="8" t="n">
+      <c r="M133" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
@@ -13578,7 +13578,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O133" s="7" t="inlineStr">
+      <c r="O133" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13662,12 +13662,12 @@
       <c r="K134" s="4" t="n">
         <v>-11</v>
       </c>
-      <c r="L134" s="7" t="inlineStr">
+      <c r="L134" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M134" s="8" t="n">
+      <c r="M134" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
@@ -13675,7 +13675,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O134" s="7" t="inlineStr">
+      <c r="O134" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,20 +13751,20 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L135" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M135" s="8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M135" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
@@ -13772,7 +13772,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O135" s="7" t="inlineStr">
+      <c r="O135" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13795,11 +13795,11 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" s="9" t="n">
-        <v>0</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X135" s="10" t="n">
         <v>7</v>
@@ -13856,12 +13856,12 @@
       <c r="K136" s="4" t="n">
         <v>-27</v>
       </c>
-      <c r="L136" s="7" t="inlineStr">
+      <c r="L136" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M136" s="8" t="n">
+      <c r="M136" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
@@ -13869,7 +13869,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O136" s="7" t="inlineStr">
+      <c r="O136" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13953,12 +13953,12 @@
       <c r="K137" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L137" s="7" t="inlineStr">
+      <c r="L137" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M137" s="8" t="n">
+      <c r="M137" s="7" t="n">
         <v>46387</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
@@ -13966,7 +13966,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O137" s="7" t="inlineStr">
+      <c r="O137" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14050,12 +14050,12 @@
       <c r="K138" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L138" s="7" t="inlineStr">
+      <c r="L138" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M138" s="8" t="n">
+      <c r="M138" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
@@ -14063,7 +14063,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O138" s="7" t="inlineStr">
+      <c r="O138" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14152,7 +14152,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M139" s="8" t="n">
+      <c r="M139" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
@@ -14160,7 +14160,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O139" s="7" t="inlineStr">
+      <c r="O139" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14249,7 +14249,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M140" s="8" t="n">
+      <c r="M140" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
@@ -14257,7 +14257,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O140" s="7" t="inlineStr">
+      <c r="O140" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14346,7 +14346,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M141" s="8" t="n">
+      <c r="M141" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N141" s="4" t="inlineStr">
@@ -14354,7 +14354,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O141" s="7" t="inlineStr">
+      <c r="O141" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14433,17 +14433,17 @@
         <v>10</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L142" s="7" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L142" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M142" s="8" t="n">
+      <c r="M142" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
@@ -14451,7 +14451,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O142" s="7" t="inlineStr">
+      <c r="O142" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14540,7 +14540,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M143" s="8" t="n">
+      <c r="M143" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
@@ -14548,7 +14548,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O143" s="7" t="inlineStr">
+      <c r="O143" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14637,7 +14637,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M144" s="8" t="n">
+      <c r="M144" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N144" s="4" t="inlineStr">
@@ -14645,7 +14645,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O144" s="7" t="inlineStr">
+      <c r="O144" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14729,12 +14729,12 @@
       <c r="K145" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="L145" s="7" t="inlineStr">
+      <c r="L145" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M145" s="8" t="n">
+      <c r="M145" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
@@ -14742,13 +14742,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O145" s="7" t="inlineStr">
+      <c r="O145" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>0</v>
@@ -14826,12 +14826,12 @@
       <c r="K146" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="L146" s="7" t="inlineStr">
+      <c r="L146" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M146" s="8" t="n">
+      <c r="M146" s="7" t="n">
         <v>46387</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
@@ -14839,7 +14839,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O146" s="7" t="inlineStr">
+      <c r="O146" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14923,12 +14923,12 @@
       <c r="K147" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="L147" s="7" t="inlineStr">
+      <c r="L147" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M147" s="8" t="n">
+      <c r="M147" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N147" s="4" t="inlineStr">
@@ -14936,7 +14936,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O147" s="7" t="inlineStr">
+      <c r="O147" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15025,7 +15025,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M148" s="8" t="n">
+      <c r="M148" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N148" s="4" t="inlineStr">
@@ -15033,7 +15033,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O148" s="7" t="inlineStr">
+      <c r="O148" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15109,20 +15109,20 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L149" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M149" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N149" s="4" t="inlineStr">
@@ -15130,7 +15130,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O149" s="7" t="inlineStr">
+      <c r="O149" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15153,11 +15153,11 @@
       <c r="U149" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="V149" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W149" s="9" t="n">
-        <v>0</v>
+      <c r="V149" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W149" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X149" s="10" t="n">
         <v>6</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,20 +15206,20 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M150" s="8" t="n">
+      <c r="M150" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N150" s="4" t="inlineStr">
@@ -15227,7 +15227,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O150" s="7" t="inlineStr">
+      <c r="O150" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15236,7 +15236,7 @@
         <v>3</v>
       </c>
       <c r="Q150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R150" s="9" t="n">
         <v>0</v>
@@ -15250,11 +15250,11 @@
       <c r="U150" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="V150" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W150" s="9" t="n">
-        <v>0</v>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W150" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>7</v>
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15303,20 +15303,20 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L151" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M151" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M151" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N151" s="4" t="inlineStr">
@@ -15324,7 +15324,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O151" s="7" t="inlineStr">
+      <c r="O151" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15347,11 +15347,11 @@
       <c r="U151" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W151" s="9" t="n">
-        <v>0</v>
+      <c r="V151" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W151" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X151" s="10" t="n">
         <v>7</v>
@@ -15400,20 +15400,20 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L152" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M152" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N152" s="4" t="inlineStr">
@@ -15421,7 +15421,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O152" s="7" t="inlineStr">
+      <c r="O152" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15430,7 +15430,7 @@
         <v>1</v>
       </c>
       <c r="Q152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R152" s="9" t="n">
         <v>0</v>
@@ -15445,7 +15445,7 @@
         <v>1</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15497,20 +15497,20 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L153" s="7" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L153" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M153" s="8" t="n">
+      <c r="M153" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N153" s="4" t="inlineStr">
@@ -15518,22 +15518,22 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O153" s="7" t="inlineStr">
+      <c r="O153" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P153" s="9" t="n">
+      <c r="P153" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="Q153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S153" s="10" t="n">
-        <v>2</v>
       </c>
       <c r="T153" s="9" t="n">
         <v>0</v>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15594,20 +15594,20 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L154" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M154" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M154" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N154" s="4" t="inlineStr">
@@ -15615,13 +15615,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O154" s="7" t="inlineStr">
+      <c r="O154" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q154" s="9" t="n">
         <v>0</v>
@@ -15638,11 +15638,11 @@
       <c r="U154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V154" s="9" t="n">
-        <v>0</v>
+      <c r="V154" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W154" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X154" s="10" t="n">
         <v>6</v>
@@ -15677,7 +15677,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -15691,20 +15691,20 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L155" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M155" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M155" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
@@ -15712,7 +15712,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O155" s="7" t="inlineStr">
+      <c r="O155" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15735,11 +15735,11 @@
       <c r="U155" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="V155" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W155" s="9" t="n">
-        <v>0</v>
+      <c r="V155" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W155" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="X155" s="10" t="n">
         <v>7</v>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15788,20 +15788,20 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L156" s="7" t="inlineStr">
+        <v>-11</v>
+      </c>
+      <c r="L156" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M156" s="8" t="n">
+      <c r="M156" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N156" s="4" t="inlineStr">
@@ -15809,7 +15809,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O156" s="7" t="inlineStr">
+      <c r="O156" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15832,8 +15832,8 @@
       <c r="U156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V156" s="9" t="n">
-        <v>0</v>
+      <c r="V156" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -15898,7 +15898,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M157" s="8" t="n">
+      <c r="M157" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N157" s="4" t="inlineStr">
@@ -15906,7 +15906,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O157" s="7" t="inlineStr">
+      <c r="O157" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15968,7 +15968,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -15982,20 +15982,20 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M158" s="8" t="n">
+      <c r="M158" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N158" s="4" t="inlineStr">
@@ -16003,7 +16003,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O158" s="7" t="inlineStr">
+      <c r="O158" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16011,8 +16011,8 @@
       <c r="P158" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Q158" s="9" t="n">
-        <v>1</v>
+      <c r="Q158" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R158" s="9" t="n">
         <v>0</v>
@@ -16030,7 +16030,7 @@
         <v>4</v>
       </c>
       <c r="W158" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X158" s="10" t="n">
         <v>7</v>
@@ -16092,7 +16092,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M159" s="8" t="n">
+      <c r="M159" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N159" s="4" t="inlineStr">
@@ -16100,7 +16100,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O159" s="7" t="inlineStr">
+      <c r="O159" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16184,12 +16184,12 @@
       <c r="K160" s="4" t="n">
         <v>-7</v>
       </c>
-      <c r="L160" s="7" t="inlineStr">
+      <c r="L160" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M160" s="8" t="n">
+      <c r="M160" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N160" s="4" t="inlineStr">
@@ -16197,7 +16197,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O160" s="7" t="inlineStr">
+      <c r="O160" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16273,20 +16273,20 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L161" s="7" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L161" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M161" s="8" t="n">
+      <c r="M161" s="7" t="n">
         <v>46446</v>
       </c>
       <c r="N161" s="4" t="inlineStr">
@@ -16294,7 +16294,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O161" s="7" t="inlineStr">
+      <c r="O161" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16424,7 +16424,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16439,7 +16439,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -16457,13 +16457,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -16490,13 +16490,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16571,7 +16571,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -16622,13 +16622,13 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -16721,7 +16721,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16820,13 +16820,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -17051,13 +17051,13 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -17066,7 +17066,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -17084,7 +17084,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -17117,7 +17117,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -17249,13 +17249,13 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -17282,7 +17282,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17315,7 +17315,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -17348,13 +17348,13 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -17447,13 +17447,13 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E33" t="n">
         <v>4</v>
       </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -17462,7 +17462,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -17480,13 +17480,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -17495,7 +17495,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -17513,7 +17513,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
